--- a/reports/2026-08_月次実績報告/excel/第51期下期境港営業所担当者別実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期下期境港営業所担当者別実績.xlsx
@@ -10379,15 +10379,15 @@
         <v/>
       </c>
       <c r="V117" s="124">
-        <f>V103-V61</f>
+        <f>V89-V19</f>
         <v/>
       </c>
       <c r="W117" s="124">
-        <f>W103-W61</f>
+        <f>W89-W19</f>
         <v/>
       </c>
       <c r="X117" s="124">
-        <f>X103-X61</f>
+        <f>X89-X19</f>
         <v/>
       </c>
       <c r="Y117" s="125">
@@ -10469,15 +10469,15 @@
         <v/>
       </c>
       <c r="V118" s="131">
-        <f>V104-V62</f>
+        <f>V90-V20</f>
         <v/>
       </c>
       <c r="W118" s="131">
-        <f>W104-W62</f>
+        <f>W90-W20</f>
         <v/>
       </c>
       <c r="X118" s="131">
-        <f>X104-X62</f>
+        <f>X90-X20</f>
         <v/>
       </c>
       <c r="Y118" s="125">
@@ -10559,15 +10559,15 @@
         <v/>
       </c>
       <c r="V119" s="131">
-        <f>V105-V63</f>
+        <f>V91-V21</f>
         <v/>
       </c>
       <c r="W119" s="131">
-        <f>W105-W63</f>
+        <f>W91-W21</f>
         <v/>
       </c>
       <c r="X119" s="131">
-        <f>X105-X63</f>
+        <f>X91-X21</f>
         <v/>
       </c>
       <c r="Y119" s="125">
@@ -10649,15 +10649,15 @@
         <v/>
       </c>
       <c r="V120" s="131">
-        <f>V106-V64</f>
+        <f>V92-V22</f>
         <v/>
       </c>
       <c r="W120" s="131">
-        <f>W106-W64</f>
+        <f>W92-W22</f>
         <v/>
       </c>
       <c r="X120" s="131">
-        <f>X106-X64</f>
+        <f>X92-X22</f>
         <v/>
       </c>
       <c r="Y120" s="125">
@@ -10739,15 +10739,15 @@
         <v/>
       </c>
       <c r="V121" s="124">
-        <f>V107-V65</f>
+        <f>V93-V23</f>
         <v/>
       </c>
       <c r="W121" s="124">
-        <f>W107-W65</f>
+        <f>W93-W23</f>
         <v/>
       </c>
       <c r="X121" s="124">
-        <f>X107-X65</f>
+        <f>X93-X23</f>
         <v/>
       </c>
       <c r="Y121" s="125">
@@ -10829,15 +10829,15 @@
         <v/>
       </c>
       <c r="V122" s="124">
-        <f>V108-V66</f>
+        <f>V94-V24</f>
         <v/>
       </c>
       <c r="W122" s="124">
-        <f>W108-W66</f>
+        <f>W94-W24</f>
         <v/>
       </c>
       <c r="X122" s="124">
-        <f>X108-X66</f>
+        <f>X94-X24</f>
         <v/>
       </c>
       <c r="Y122" s="125">
@@ -10919,15 +10919,15 @@
         <v/>
       </c>
       <c r="V123" s="131">
-        <f>V109-V67</f>
+        <f>V95-V25</f>
         <v/>
       </c>
       <c r="W123" s="131">
-        <f>W109-W67</f>
+        <f>W95-W25</f>
         <v/>
       </c>
       <c r="X123" s="131">
-        <f>X109-X67</f>
+        <f>X95-X25</f>
         <v/>
       </c>
       <c r="Y123" s="125">
@@ -11009,15 +11009,15 @@
         <v/>
       </c>
       <c r="V124" s="124">
-        <f>V110-V68</f>
+        <f>V96-V26</f>
         <v/>
       </c>
       <c r="W124" s="124">
-        <f>W110-W68</f>
+        <f>W96-W26</f>
         <v/>
       </c>
       <c r="X124" s="124">
-        <f>X110-X68</f>
+        <f>X96-X26</f>
         <v/>
       </c>
       <c r="Y124" s="125">
@@ -11099,15 +11099,15 @@
         <v/>
       </c>
       <c r="V125" s="124">
-        <f>V111-V69</f>
+        <f>V97-V27</f>
         <v/>
       </c>
       <c r="W125" s="124">
-        <f>W111-W69</f>
+        <f>W97-W27</f>
         <v/>
       </c>
       <c r="X125" s="124">
-        <f>X111-X69</f>
+        <f>X97-X27</f>
         <v/>
       </c>
       <c r="Y125" s="125">
@@ -19566,11 +19566,11 @@
         <v/>
       </c>
       <c r="V117" s="124">
-        <f>V103-V61</f>
+        <f>V89-V19</f>
         <v/>
       </c>
       <c r="W117" s="124">
-        <f>W103-W61</f>
+        <f>W89-W19</f>
         <v/>
       </c>
       <c r="X117" s="124" t="n"/>
@@ -19653,11 +19653,11 @@
         <v/>
       </c>
       <c r="V118" s="124">
-        <f>V104-V62</f>
+        <f>V90-V20</f>
         <v/>
       </c>
       <c r="W118" s="124">
-        <f>W104-W62</f>
+        <f>W90-W20</f>
         <v/>
       </c>
       <c r="X118" s="124" t="n"/>
@@ -19740,11 +19740,11 @@
         <v/>
       </c>
       <c r="V119" s="124">
-        <f>V105-V63</f>
+        <f>V91-V21</f>
         <v/>
       </c>
       <c r="W119" s="124">
-        <f>W105-W63</f>
+        <f>W91-W21</f>
         <v/>
       </c>
       <c r="X119" s="124" t="n"/>
@@ -19827,11 +19827,11 @@
         <v/>
       </c>
       <c r="V120" s="124">
-        <f>V106-V64</f>
+        <f>V92-V22</f>
         <v/>
       </c>
       <c r="W120" s="124">
-        <f>W106-W64</f>
+        <f>W92-W22</f>
         <v/>
       </c>
       <c r="X120" s="124" t="n"/>
@@ -19914,11 +19914,11 @@
         <v/>
       </c>
       <c r="V121" s="124">
-        <f>V107-V65</f>
+        <f>V93-V23</f>
         <v/>
       </c>
       <c r="W121" s="124">
-        <f>W107-W65</f>
+        <f>W93-W23</f>
         <v/>
       </c>
       <c r="X121" s="124" t="n"/>
@@ -20001,11 +20001,11 @@
         <v/>
       </c>
       <c r="V122" s="124">
-        <f>V108-V66</f>
+        <f>V94-V24</f>
         <v/>
       </c>
       <c r="W122" s="124">
-        <f>W108-W66</f>
+        <f>W94-W24</f>
         <v/>
       </c>
       <c r="X122" s="124" t="n"/>
@@ -20088,11 +20088,11 @@
         <v/>
       </c>
       <c r="V123" s="124">
-        <f>V109-V67</f>
+        <f>V95-V25</f>
         <v/>
       </c>
       <c r="W123" s="124">
-        <f>W109-W67</f>
+        <f>W95-W25</f>
         <v/>
       </c>
       <c r="X123" s="124" t="n"/>
@@ -20175,11 +20175,11 @@
         <v/>
       </c>
       <c r="V124" s="124">
-        <f>V110-V68</f>
+        <f>V96-V26</f>
         <v/>
       </c>
       <c r="W124" s="124">
-        <f>W110-W68</f>
+        <f>W96-W26</f>
         <v/>
       </c>
       <c r="X124" s="124" t="n"/>
@@ -20262,11 +20262,11 @@
         <v/>
       </c>
       <c r="V125" s="124">
-        <f>V111-V69</f>
+        <f>V97-V27</f>
         <v/>
       </c>
       <c r="W125" s="124">
-        <f>W111-W69</f>
+        <f>W97-W27</f>
         <v/>
       </c>
       <c r="X125" s="124" t="n"/>
@@ -27853,15 +27853,15 @@
         <v/>
       </c>
       <c r="T103" s="139">
-        <f>T75-T5</f>
+        <f>T89-T47</f>
         <v/>
       </c>
       <c r="U103" s="139">
-        <f>U75-U5</f>
+        <f>U89-U47</f>
         <v/>
       </c>
       <c r="V103" s="139">
-        <f>V75-V5</f>
+        <f>V89-V47</f>
         <v/>
       </c>
       <c r="W103" s="139">
@@ -27943,15 +27943,15 @@
         <v/>
       </c>
       <c r="T104" s="139">
-        <f>T76-T6</f>
+        <f>T90-T48</f>
         <v/>
       </c>
       <c r="U104" s="139">
-        <f>U76-U6</f>
+        <f>U90-U48</f>
         <v/>
       </c>
       <c r="V104" s="139">
-        <f>V76-V6</f>
+        <f>V90-V48</f>
         <v/>
       </c>
       <c r="W104" s="139">
@@ -28033,15 +28033,15 @@
         <v/>
       </c>
       <c r="T105" s="139">
-        <f>T77-T7</f>
+        <f>T91-T49</f>
         <v/>
       </c>
       <c r="U105" s="139">
-        <f>U77-U7</f>
+        <f>U91-U49</f>
         <v/>
       </c>
       <c r="V105" s="139">
-        <f>V77-V7</f>
+        <f>V91-V49</f>
         <v/>
       </c>
       <c r="W105" s="139">
@@ -28123,15 +28123,15 @@
         <v/>
       </c>
       <c r="T106" s="139">
-        <f>T78-T8</f>
+        <f>T92-T50</f>
         <v/>
       </c>
       <c r="U106" s="139">
-        <f>U78-U8</f>
+        <f>U92-U50</f>
         <v/>
       </c>
       <c r="V106" s="139">
-        <f>V78-V8</f>
+        <f>V92-V50</f>
         <v/>
       </c>
       <c r="W106" s="139">
@@ -28213,15 +28213,15 @@
         <v/>
       </c>
       <c r="T107" s="139">
-        <f>T79-T9</f>
+        <f>T93-T51</f>
         <v/>
       </c>
       <c r="U107" s="139">
-        <f>U79-U9</f>
+        <f>U93-U51</f>
         <v/>
       </c>
       <c r="V107" s="139">
-        <f>V79-V9</f>
+        <f>V93-V51</f>
         <v/>
       </c>
       <c r="W107" s="139">
@@ -28303,15 +28303,15 @@
         <v/>
       </c>
       <c r="T108" s="139">
-        <f>T80-T10</f>
+        <f>T94-T52</f>
         <v/>
       </c>
       <c r="U108" s="139">
-        <f>U80-U10</f>
+        <f>U94-U52</f>
         <v/>
       </c>
       <c r="V108" s="139">
-        <f>V80-V10</f>
+        <f>V94-V52</f>
         <v/>
       </c>
       <c r="W108" s="139">
@@ -28393,15 +28393,15 @@
         <v/>
       </c>
       <c r="T109" s="139">
-        <f>T81-T11</f>
+        <f>T95-T53</f>
         <v/>
       </c>
       <c r="U109" s="139">
-        <f>U81-U11</f>
+        <f>U95-U53</f>
         <v/>
       </c>
       <c r="V109" s="139">
-        <f>V81-V11</f>
+        <f>V95-V53</f>
         <v/>
       </c>
       <c r="W109" s="139">
@@ -28483,15 +28483,15 @@
         <v/>
       </c>
       <c r="T110" s="139">
-        <f>T82-T12</f>
+        <f>T96-T54</f>
         <v/>
       </c>
       <c r="U110" s="139">
-        <f>U82-U12</f>
+        <f>U96-U54</f>
         <v/>
       </c>
       <c r="V110" s="139">
-        <f>V82-V12</f>
+        <f>V96-V54</f>
         <v/>
       </c>
       <c r="W110" s="139">
@@ -28573,15 +28573,15 @@
         <v/>
       </c>
       <c r="T111" s="139">
-        <f>T83-T13</f>
+        <f>T97-T55</f>
         <v/>
       </c>
       <c r="U111" s="139">
-        <f>U83-U13</f>
+        <f>U97-U55</f>
         <v/>
       </c>
       <c r="V111" s="139">
-        <f>V83-V13</f>
+        <f>V97-V55</f>
         <v/>
       </c>
       <c r="W111" s="139">
